--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -62,7 +62,7 @@
     <t>7,33,18,2004,2003</t>
   </si>
   <si>
-    <t>40,40,40,40,40</t>
+    <t>35,35,35,35,35</t>
   </si>
   <si>
     <t>法魂</t>
@@ -1257,7 +1257,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 D4 E4 F4 D5 E5 F5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:F3 E4:F4 E5:F5 C3:C5 D4:D5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -62,7 +62,7 @@
     <t>7,33,18,2004,2003</t>
   </si>
   <si>
-    <t>35,35,35,35,35</t>
+    <t>40,40,40,40,40</t>
   </si>
   <si>
     <t>法魂</t>
@@ -1257,7 +1257,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:F3 E4:F4 E5:F5 C3:C5 D4:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="54">
   <si>
     <t>ID</t>
   </si>
@@ -56,7 +56,7 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>战魂</t>
+    <t>橙色战魂40</t>
   </si>
   <si>
     <t>7,33,18,2004,2003</t>
@@ -65,16 +65,130 @@
     <t>40,40,40,40,40</t>
   </si>
   <si>
-    <t>法魂</t>
+    <t>橙色法魂40</t>
   </si>
   <si>
     <t>7,34,18,2005,2003</t>
   </si>
   <si>
-    <t>道魂</t>
+    <t>橙色道魂40</t>
   </si>
   <si>
     <t>7,35,18,2006,2003</t>
+  </si>
+  <si>
+    <t>橙色战魂45</t>
+  </si>
+  <si>
+    <t>45,45,45,45,45</t>
+  </si>
+  <si>
+    <t>橙色法魂45</t>
+  </si>
+  <si>
+    <t>橙色道魂45</t>
+  </si>
+  <si>
+    <t>橙色战魂50</t>
+  </si>
+  <si>
+    <t>50,50,50,50,50</t>
+  </si>
+  <si>
+    <t>橙色法魂50</t>
+  </si>
+  <si>
+    <t>橙色道魂50</t>
+  </si>
+  <si>
+    <t>红色战魂40</t>
+  </si>
+  <si>
+    <t>7,33,18,2004,2003,2001</t>
+  </si>
+  <si>
+    <t>40,40,40,40,40,40</t>
+  </si>
+  <si>
+    <t>红色法魂40</t>
+  </si>
+  <si>
+    <t>7,34,18,2005,2003,2001</t>
+  </si>
+  <si>
+    <t>红色道魂40</t>
+  </si>
+  <si>
+    <t>7,35,18,2006,2003,2001</t>
+  </si>
+  <si>
+    <t>红色战魂45</t>
+  </si>
+  <si>
+    <t>45,45,45,45,45,45</t>
+  </si>
+  <si>
+    <t>红色法魂45</t>
+  </si>
+  <si>
+    <t>红色道魂45</t>
+  </si>
+  <si>
+    <t>红色战魂50</t>
+  </si>
+  <si>
+    <t>50,50,50,50,50,50</t>
+  </si>
+  <si>
+    <t>红色法魂50</t>
+  </si>
+  <si>
+    <t>红色道魂50</t>
+  </si>
+  <si>
+    <t>金色战魂40</t>
+  </si>
+  <si>
+    <t>7,33,18,2004,2003,2001,21</t>
+  </si>
+  <si>
+    <t>40,40,40,40,40,40,40</t>
+  </si>
+  <si>
+    <t>金色法魂40</t>
+  </si>
+  <si>
+    <t>7,34,18,2005,2003,2001,21</t>
+  </si>
+  <si>
+    <t>金色道魂40</t>
+  </si>
+  <si>
+    <t>7,35,18,2006,2003,2001,21</t>
+  </si>
+  <si>
+    <t>金色战魂45</t>
+  </si>
+  <si>
+    <t>45,45,45,45,45,45,45</t>
+  </si>
+  <si>
+    <t>金色法魂45</t>
+  </si>
+  <si>
+    <t>金色道魂45</t>
+  </si>
+  <si>
+    <t>金色战魂50</t>
+  </si>
+  <si>
+    <t>50,50,50,50,50,50,50</t>
+  </si>
+  <si>
+    <t>金色法魂50</t>
+  </si>
+  <si>
+    <t>金色道魂50</t>
   </si>
 </sst>
 </file>
@@ -1051,7 +1165,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
@@ -1181,32 +1295,416 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1"/>
-    <row r="10" s="2" customFormat="1" customHeight="1"/>
-    <row r="11" s="2" customFormat="1" customHeight="1"/>
-    <row r="12" s="2" customFormat="1" customHeight="1"/>
-    <row r="13" s="2" customFormat="1" customHeight="1"/>
-    <row r="14" s="2" customFormat="1" customHeight="1"/>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C9" s="2">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C11" s="2">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C12" s="2">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C13" s="2">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C14" s="2">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="2">
+        <v>3</v>
+      </c>
+    </row>
     <row r="15" s="2" customFormat="1" customHeight="1"/>
-    <row r="16" s="2" customFormat="1" customHeight="1"/>
-    <row r="17" s="2" customFormat="1" customHeight="1"/>
-    <row r="18" s="2" customFormat="1" customHeight="1"/>
-    <row r="19" s="2" customFormat="1" customHeight="1"/>
-    <row r="20" s="2" customFormat="1" customHeight="1"/>
-    <row r="21" s="2" customFormat="1" customHeight="1"/>
-    <row r="22" s="2" customFormat="1" customHeight="1"/>
-    <row r="23" s="2" customFormat="1" customHeight="1"/>
-    <row r="24" s="2" customFormat="1" customHeight="1"/>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C16" s="2">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C17" s="2">
+        <v>11</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C18" s="2">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C19" s="2">
+        <v>13</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C20" s="2">
+        <v>14</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C21" s="2">
+        <v>15</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C22" s="2">
+        <v>16</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C23" s="2">
+        <v>17</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C24" s="2">
+        <v>18</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G24" s="2">
+        <v>3</v>
+      </c>
+    </row>
     <row r="25" s="2" customFormat="1" customHeight="1"/>
-    <row r="26" s="2" customFormat="1" customHeight="1"/>
-    <row r="27" s="2" customFormat="1" customHeight="1"/>
-    <row r="28" s="2" customFormat="1" customHeight="1"/>
-    <row r="29" s="2" customFormat="1" customHeight="1"/>
-    <row r="30" s="2" customFormat="1" customHeight="1"/>
-    <row r="31" s="2" customFormat="1" customHeight="1"/>
-    <row r="32" s="2" customFormat="1" customHeight="1"/>
-    <row r="33" s="2" customFormat="1" customHeight="1"/>
-    <row r="34" s="2" customFormat="1" customHeight="1"/>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C26" s="2">
+        <v>19</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C27" s="2">
+        <v>20</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C28" s="2">
+        <v>21</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G28" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C29" s="2">
+        <v>22</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C30" s="2">
+        <v>23</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G30" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C31" s="2">
+        <v>24</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G31" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C32" s="2">
+        <v>25</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G32" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C33" s="2">
+        <v>26</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G33" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C34" s="2">
+        <v>27</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G34" s="2">
+        <v>3</v>
+      </c>
+    </row>
     <row r="35" s="2" customFormat="1" customHeight="1"/>
     <row r="36" s="2" customFormat="1" customHeight="1"/>
     <row r="37" s="2" customFormat="1" customHeight="1"/>
@@ -1219,24 +1717,12 @@
     <row r="44" s="2" customFormat="1" customHeight="1"/>
     <row r="45" s="2" customFormat="1" customHeight="1"/>
     <row r="46" s="2" customFormat="1" customHeight="1"/>
-    <row r="62" customHeight="1" spans="7:7">
-      <c r="G62" s="6"/>
-    </row>
-    <row r="63" customHeight="1" spans="7:7">
-      <c r="G63" s="6"/>
-    </row>
-    <row r="64" customHeight="1" spans="7:7">
-      <c r="G64" s="6"/>
-    </row>
-    <row r="65" customHeight="1" spans="7:7">
-      <c r="G65" s="6"/>
-    </row>
-    <row r="66" customHeight="1" spans="7:7">
-      <c r="G66" s="6"/>
-    </row>
-    <row r="67" customHeight="1" spans="7:7">
-      <c r="G67" s="6"/>
-    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1"/>
+    <row r="48" s="2" customFormat="1" customHeight="1"/>
+    <row r="49" s="2" customFormat="1" customHeight="1"/>
+    <row r="50" s="2" customFormat="1" customHeight="1"/>
+    <row r="51" s="2" customFormat="1" customHeight="1"/>
+    <row r="52" s="2" customFormat="1" customHeight="1"/>
     <row r="68" customHeight="1" spans="7:7">
       <c r="G68" s="6"/>
     </row>
@@ -1246,14 +1732,32 @@
     <row r="70" customHeight="1" spans="7:7">
       <c r="G70" s="6"/>
     </row>
-    <row r="87" customHeight="1" spans="7:7">
-      <c r="G87" s="6"/>
-    </row>
-    <row r="88" customHeight="1" spans="7:7">
-      <c r="G88" s="6"/>
-    </row>
-    <row r="89" customHeight="1" spans="7:7">
-      <c r="G89" s="6"/>
+    <row r="71" customHeight="1" spans="7:7">
+      <c r="G71" s="6"/>
+    </row>
+    <row r="72" customHeight="1" spans="7:7">
+      <c r="G72" s="6"/>
+    </row>
+    <row r="73" customHeight="1" spans="7:7">
+      <c r="G73" s="6"/>
+    </row>
+    <row r="74" customHeight="1" spans="7:7">
+      <c r="G74" s="6"/>
+    </row>
+    <row r="75" customHeight="1" spans="7:7">
+      <c r="G75" s="6"/>
+    </row>
+    <row r="76" customHeight="1" spans="7:7">
+      <c r="G76" s="6"/>
+    </row>
+    <row r="93" customHeight="1" spans="7:7">
+      <c r="G93" s="6"/>
+    </row>
+    <row r="94" customHeight="1" spans="7:7">
+      <c r="G94" s="6"/>
+    </row>
+    <row r="95" customHeight="1" spans="7:7">
+      <c r="G95" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -149,7 +149,7 @@
     <t>金色战魂40</t>
   </si>
   <si>
-    <t>7,33,18,2004,2003,2001,21</t>
+    <t>7,33,18,2004,2003,2001,50</t>
   </si>
   <si>
     <t>40,40,40,40,40,40,40</t>
@@ -158,13 +158,13 @@
     <t>金色法魂40</t>
   </si>
   <si>
-    <t>7,34,18,2005,2003,2001,21</t>
+    <t>7,34,18,2005,2003,2001,50</t>
   </si>
   <si>
     <t>金色道魂40</t>
   </si>
   <si>
-    <t>7,35,18,2006,2003,2001,21</t>
+    <t>7,35,18,2006,2003,2001,50</t>
   </si>
   <si>
     <t>金色战魂45</t>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -149,7 +149,7 @@
     <t>金色战魂40</t>
   </si>
   <si>
-    <t>7,33,18,2004,2003,2001,50</t>
+    <t>8,33,18,2004,2003,2001,50</t>
   </si>
   <si>
     <t>40,40,40,40,40,40,40</t>
@@ -158,13 +158,13 @@
     <t>金色法魂40</t>
   </si>
   <si>
-    <t>7,34,18,2005,2003,2001,50</t>
+    <t>8,34,18,2005,2003,2001,50</t>
   </si>
   <si>
     <t>金色道魂40</t>
   </si>
   <si>
-    <t>7,35,18,2006,2003,2001,50</t>
+    <t>8,35,18,2006,2003,2001,50</t>
   </si>
   <si>
     <t>金色战魂45</t>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="57">
   <si>
     <t>ID</t>
   </si>
@@ -189,6 +189,15 @@
   </si>
   <si>
     <t>金色道魂50</t>
+  </si>
+  <si>
+    <t>7,33,18,2004,2003,2001,50</t>
+  </si>
+  <si>
+    <t>7,34,18,2005,2003,2001,50</t>
+  </si>
+  <si>
+    <t>7,35,18,2006,2003,2001,50</t>
   </si>
 </sst>
 </file>
@@ -1705,15 +1714,159 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" s="2" customFormat="1" customHeight="1"/>
-    <row r="36" s="2" customFormat="1" customHeight="1"/>
-    <row r="37" s="2" customFormat="1" customHeight="1"/>
-    <row r="38" s="2" customFormat="1" customHeight="1"/>
-    <row r="39" s="2" customFormat="1" customHeight="1"/>
-    <row r="40" s="2" customFormat="1" customHeight="1"/>
-    <row r="41" s="2" customFormat="1" customHeight="1"/>
-    <row r="42" s="2" customFormat="1" customHeight="1"/>
-    <row r="43" s="2" customFormat="1" customHeight="1"/>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C35" s="2">
+        <v>28</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G35" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C36" s="2">
+        <v>29</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G36" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C37" s="2">
+        <v>30</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G37" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C38" s="2">
+        <v>31</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G38" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C39" s="2">
+        <v>32</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G39" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C40" s="2">
+        <v>33</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G40" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C41" s="2">
+        <v>34</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C42" s="2">
+        <v>35</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G42" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C43" s="2">
+        <v>36</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G43" s="2">
+        <v>3</v>
+      </c>
+    </row>
     <row r="44" s="2" customFormat="1" customHeight="1"/>
     <row r="45" s="2" customFormat="1" customHeight="1"/>
     <row r="46" s="2" customFormat="1" customHeight="1"/>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="60">
   <si>
     <t>ID</t>
   </si>
@@ -198,6 +198,15 @@
   </si>
   <si>
     <t>7,35,18,2006,2003,2001,50</t>
+  </si>
+  <si>
+    <t>7,33,18,2004,2003,32,50</t>
+  </si>
+  <si>
+    <t>7,34,18,2005,2003,32,50</t>
+  </si>
+  <si>
+    <t>7,35,18,2006,2003,32,50</t>
   </si>
 </sst>
 </file>
@@ -1867,15 +1876,159 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" s="2" customFormat="1" customHeight="1"/>
-    <row r="45" s="2" customFormat="1" customHeight="1"/>
-    <row r="46" s="2" customFormat="1" customHeight="1"/>
-    <row r="47" s="2" customFormat="1" customHeight="1"/>
-    <row r="48" s="2" customFormat="1" customHeight="1"/>
-    <row r="49" s="2" customFormat="1" customHeight="1"/>
-    <row r="50" s="2" customFormat="1" customHeight="1"/>
-    <row r="51" s="2" customFormat="1" customHeight="1"/>
-    <row r="52" s="2" customFormat="1" customHeight="1"/>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C44" s="2">
+        <v>37</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G44" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C45" s="2">
+        <v>38</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G45" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C46" s="2">
+        <v>39</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G46" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C47" s="2">
+        <v>40</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G47" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C48" s="2">
+        <v>41</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G48" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C49" s="2">
+        <v>42</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G49" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C50" s="2">
+        <v>43</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G50" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C51" s="2">
+        <v>44</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G51" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C52" s="2">
+        <v>45</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G52" s="2">
+        <v>3</v>
+      </c>
+    </row>
     <row r="68" customHeight="1" spans="7:7">
       <c r="G68" s="6"/>
     </row>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="59">
   <si>
     <t>ID</t>
   </si>
@@ -167,16 +167,31 @@
     <t>8,35,18,2006,2003,2001,50</t>
   </si>
   <si>
-    <t>金色战魂45</t>
-  </si>
-  <si>
-    <t>45,45,45,45,45,45,45</t>
-  </si>
-  <si>
-    <t>金色法魂45</t>
-  </si>
-  <si>
-    <t>金色道魂45</t>
+    <t>7,33,18,2004,2003,2001,50</t>
+  </si>
+  <si>
+    <t>7,34,18,2005,2003,2001,50</t>
+  </si>
+  <si>
+    <t>7,35,18,2006,2003,2001,50</t>
+  </si>
+  <si>
+    <t>8,33,18,2004,2003,32,50</t>
+  </si>
+  <si>
+    <t>8,34,18,2005,2003,32,50</t>
+  </si>
+  <si>
+    <t>8,35,18,2006,2003,32,50</t>
+  </si>
+  <si>
+    <t>7,33,18,2004,2003,32,50</t>
+  </si>
+  <si>
+    <t>7,34,18,2005,2003,32,50</t>
+  </si>
+  <si>
+    <t>7,35,18,2006,2003,32,50</t>
   </si>
   <si>
     <t>金色战魂50</t>
@@ -189,24 +204,6 @@
   </si>
   <si>
     <t>金色道魂50</t>
-  </si>
-  <si>
-    <t>7,33,18,2004,2003,2001,50</t>
-  </si>
-  <si>
-    <t>7,34,18,2005,2003,2001,50</t>
-  </si>
-  <si>
-    <t>7,35,18,2006,2003,2001,50</t>
-  </si>
-  <si>
-    <t>7,33,18,2004,2003,32,50</t>
-  </si>
-  <si>
-    <t>7,34,18,2005,2003,32,50</t>
-  </si>
-  <si>
-    <t>7,35,18,2006,2003,32,50</t>
   </si>
 </sst>
 </file>
@@ -1183,7 +1180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
@@ -1626,13 +1623,13 @@
         <v>22</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="7" t="s">
-        <v>40</v>
-      </c>
       <c r="F29" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -1643,13 +1640,13 @@
         <v>23</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G30" s="2">
         <v>2</v>
@@ -1660,13 +1657,13 @@
         <v>24</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G31" s="2">
         <v>3</v>
@@ -1677,13 +1674,13 @@
         <v>25</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -1694,13 +1691,13 @@
         <v>26</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G33" s="2">
         <v>2</v>
@@ -1711,13 +1708,13 @@
         <v>27</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G34" s="2">
         <v>3</v>
@@ -1731,7 +1728,7 @@
         <v>39</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>41</v>
@@ -1748,7 +1745,7 @@
         <v>42</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>41</v>
@@ -1765,7 +1762,7 @@
         <v>44</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>41</v>
@@ -1779,13 +1776,13 @@
         <v>31</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -1796,13 +1793,13 @@
         <v>32</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G39" s="2">
         <v>2</v>
@@ -1813,13 +1810,13 @@
         <v>33</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E40" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>56</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="G40" s="2">
         <v>3</v>
@@ -1830,13 +1827,13 @@
         <v>34</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -1847,13 +1844,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G42" s="2">
         <v>2</v>
@@ -1864,13 +1861,13 @@
         <v>36</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E43" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F43" s="7" t="s">
         <v>56</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>51</v>
       </c>
       <c r="G43" s="2">
         <v>3</v>
@@ -1881,13 +1878,13 @@
         <v>37</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -1898,13 +1895,13 @@
         <v>38</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="G45" s="2">
         <v>2</v>
@@ -1915,13 +1912,13 @@
         <v>39</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="G46" s="2">
         <v>3</v>
@@ -1932,13 +1929,13 @@
         <v>40</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -1949,13 +1946,13 @@
         <v>41</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G48" s="2">
         <v>2</v>
@@ -1966,68 +1963,26 @@
         <v>42</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G49" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C50" s="2">
-        <v>43</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G50" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C51" s="2">
-        <v>44</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G51" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C52" s="2">
-        <v>45</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G52" s="2">
-        <v>3</v>
-      </c>
+    <row r="65" customHeight="1" spans="7:7">
+      <c r="G65" s="6"/>
+    </row>
+    <row r="66" customHeight="1" spans="7:7">
+      <c r="G66" s="6"/>
+    </row>
+    <row r="67" customHeight="1" spans="7:7">
+      <c r="G67" s="6"/>
     </row>
     <row r="68" customHeight="1" spans="7:7">
       <c r="G68" s="6"/>
@@ -2047,23 +2002,14 @@
     <row r="73" customHeight="1" spans="7:7">
       <c r="G73" s="6"/>
     </row>
-    <row r="74" customHeight="1" spans="7:7">
-      <c r="G74" s="6"/>
-    </row>
-    <row r="75" customHeight="1" spans="7:7">
-      <c r="G75" s="6"/>
-    </row>
-    <row r="76" customHeight="1" spans="7:7">
-      <c r="G76" s="6"/>
-    </row>
-    <row r="93" customHeight="1" spans="7:7">
-      <c r="G93" s="6"/>
-    </row>
-    <row r="94" customHeight="1" spans="7:7">
-      <c r="G94" s="6"/>
-    </row>
-    <row r="95" customHeight="1" spans="7:7">
-      <c r="G95" s="6"/>
+    <row r="90" customHeight="1" spans="7:7">
+      <c r="G90" s="6"/>
+    </row>
+    <row r="91" customHeight="1" spans="7:7">
+      <c r="G91" s="6"/>
+    </row>
+    <row r="92" customHeight="1" spans="7:7">
+      <c r="G92" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="58">
   <si>
     <t>ID</t>
   </si>
@@ -134,34 +134,31 @@
     <t>红色道魂45</t>
   </si>
   <si>
-    <t>红色战魂50</t>
-  </si>
-  <si>
-    <t>50,50,50,50,50,50</t>
-  </si>
-  <si>
-    <t>红色法魂50</t>
-  </si>
-  <si>
-    <t>红色道魂50</t>
-  </si>
-  <si>
     <t>金色战魂40</t>
   </si>
   <si>
+    <t>7,33,19,2004,2003,32,52</t>
+  </si>
+  <si>
+    <t>40,40,40,40,40,40,40</t>
+  </si>
+  <si>
+    <t>金色法魂40</t>
+  </si>
+  <si>
+    <t>7,34,19,2005,2003,32,52</t>
+  </si>
+  <si>
+    <t>金色道魂40</t>
+  </si>
+  <si>
+    <t>7,35,19,2006,2003,32,52</t>
+  </si>
+  <si>
     <t>8,33,18,2004,2003,2001,50</t>
   </si>
   <si>
-    <t>40,40,40,40,40,40,40</t>
-  </si>
-  <si>
-    <t>金色法魂40</t>
-  </si>
-  <si>
     <t>8,34,18,2005,2003,2001,50</t>
-  </si>
-  <si>
-    <t>金色道魂40</t>
   </si>
   <si>
     <t>8,35,18,2006,2003,2001,50</t>
@@ -1180,7 +1177,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
@@ -1515,468 +1512,466 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C22" s="2">
-        <v>16</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G22" s="2">
-        <v>1</v>
-      </c>
-    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1"/>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C23" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>36</v>
-      </c>
       <c r="G23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C24" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G24" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C25" s="2">
+        <v>18</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" customHeight="1"/>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C26" s="2">
-        <v>19</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1</v>
-      </c>
-    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1"/>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C27" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>43</v>
-      </c>
       <c r="F27" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C28" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G28" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C29" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G29" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C30" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C31" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G31" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C32" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G32" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C33" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G33" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C34" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G34" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C35" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G35" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C36" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C37" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G37" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C38" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="G38" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C39" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G39" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C40" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G40" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C41" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>56</v>
-      </c>
       <c r="G41" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C42" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G42" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C43" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G43" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C44" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F44" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E44" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>56</v>
-      </c>
       <c r="G44" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C45" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G45" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C46" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G46" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C47" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F47" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E47" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>56</v>
-      </c>
       <c r="G47" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C48" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C49" s="2">
+        <v>41</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G49" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C50" s="2">
         <v>42</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G49" s="2">
+      <c r="D50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G50" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="65" customHeight="1" spans="7:7">
-      <c r="G65" s="6"/>
     </row>
     <row r="66" customHeight="1" spans="7:7">
       <c r="G66" s="6"/>
@@ -2002,14 +1997,17 @@
     <row r="73" customHeight="1" spans="7:7">
       <c r="G73" s="6"/>
     </row>
-    <row r="90" customHeight="1" spans="7:7">
-      <c r="G90" s="6"/>
+    <row r="74" customHeight="1" spans="7:7">
+      <c r="G74" s="6"/>
     </row>
     <row r="91" customHeight="1" spans="7:7">
       <c r="G91" s="6"/>
     </row>
     <row r="92" customHeight="1" spans="7:7">
       <c r="G92" s="6"/>
+    </row>
+    <row r="93" customHeight="1" spans="7:7">
+      <c r="G93" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="61">
   <si>
     <t>ID</t>
   </si>
@@ -201,6 +201,15 @@
   </si>
   <si>
     <t>金色道魂50</t>
+  </si>
+  <si>
+    <t>13,33,19,2004,2003,32,52</t>
+  </si>
+  <si>
+    <t>13,34,19,2005,2003,32,52</t>
+  </si>
+  <si>
+    <t>13,35,19,2006,2003,32,52</t>
   </si>
 </sst>
 </file>
@@ -1177,7 +1186,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
@@ -1769,212 +1778,261 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C39" s="2">
-        <v>31</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G39" s="2">
-        <v>1</v>
-      </c>
-    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1"/>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C40" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C41" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G41" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C42" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G42" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C43" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C44" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G44" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C45" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G45" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C46" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G46" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C47" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G47" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C48" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G48" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C49" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G49" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C50" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G50" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C51" s="2">
+        <v>42</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G51" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="7:7">
-      <c r="G66" s="6"/>
+    <row r="52" customHeight="1" spans="3:7">
+      <c r="C52" s="2">
+        <v>43</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G52" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:7">
+      <c r="C53" s="2">
+        <v>44</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G53" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:7">
+      <c r="C54" s="2">
+        <v>45</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G54" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="67" customHeight="1" spans="7:7">
       <c r="G67" s="6"/>
@@ -2000,14 +2058,17 @@
     <row r="74" customHeight="1" spans="7:7">
       <c r="G74" s="6"/>
     </row>
-    <row r="91" customHeight="1" spans="7:7">
-      <c r="G91" s="6"/>
+    <row r="75" customHeight="1" spans="7:7">
+      <c r="G75" s="6"/>
     </row>
     <row r="92" customHeight="1" spans="7:7">
       <c r="G92" s="6"/>
     </row>
     <row r="93" customHeight="1" spans="7:7">
       <c r="G93" s="6"/>
+    </row>
+    <row r="94" customHeight="1" spans="7:7">
+      <c r="G94" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="67">
   <si>
     <t>ID</t>
   </si>
@@ -155,6 +155,24 @@
     <t>7,35,19,2006,2003,32,52</t>
   </si>
   <si>
+    <t>8,33,19,2004,2003,31,52</t>
+  </si>
+  <si>
+    <t>8,34,19,2005,2003,31,52</t>
+  </si>
+  <si>
+    <t>8,35,19,2006,2003,31,52</t>
+  </si>
+  <si>
+    <t>13,33,19,2004,2003,32,52</t>
+  </si>
+  <si>
+    <t>13,34,19,2005,2003,32,52</t>
+  </si>
+  <si>
+    <t>13,35,19,2006,2003,32,52</t>
+  </si>
+  <si>
     <t>8,33,18,2004,2003,2001,50</t>
   </si>
   <si>
@@ -203,13 +221,13 @@
     <t>金色道魂50</t>
   </si>
   <si>
-    <t>13,33,19,2004,2003,32,52</t>
-  </si>
-  <si>
-    <t>13,34,19,2005,2003,32,52</t>
-  </si>
-  <si>
-    <t>13,35,19,2006,2003,32,52</t>
+    <t>13,33,24,2004,2003,32,53</t>
+  </si>
+  <si>
+    <t>13,34,24,2005,2003,32,53</t>
+  </si>
+  <si>
+    <t>13,35,24,2006,2003,32,53</t>
   </si>
 </sst>
 </file>
@@ -1186,7 +1204,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
@@ -1573,112 +1591,112 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1"/>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C26" s="2">
+        <v>101</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+    </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C27" s="2">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>37</v>
       </c>
       <c r="G27" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C28" s="2">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>37</v>
       </c>
       <c r="G28" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C29" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>37</v>
       </c>
       <c r="G29" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C30" s="2">
-        <v>22</v>
+        <v>105</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>37</v>
       </c>
       <c r="G30" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C31" s="2">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>37</v>
       </c>
       <c r="G31" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C32" s="2">
-        <v>24</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G32" s="2">
         <v>3</v>
       </c>
     </row>
+    <row r="32" s="2" customFormat="1" customHeight="1"/>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C33" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>35</v>
@@ -1695,7 +1713,7 @@
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C34" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>38</v>
@@ -1712,7 +1730,7 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C35" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>40</v>
@@ -1729,7 +1747,7 @@
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C36" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>35</v>
@@ -1746,7 +1764,7 @@
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C37" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>38</v>
@@ -1763,7 +1781,7 @@
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C38" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>40</v>
@@ -1778,121 +1796,121 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" s="2" customFormat="1" customHeight="1"/>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C39" s="2">
+        <v>25</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G39" s="2">
+        <v>1</v>
+      </c>
+    </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C40" s="2">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="G40" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C41" s="2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E41" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E41" s="7" t="s">
-        <v>43</v>
-      </c>
       <c r="F41" s="7" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="G41" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C42" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>44</v>
-      </c>
       <c r="F42" s="7" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="G42" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C43" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="G43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C44" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="G44" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C45" s="2">
-        <v>36</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G45" s="2">
         <v>3</v>
       </c>
     </row>
+    <row r="45" s="2" customFormat="1" customHeight="1"/>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C46" s="2">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -1900,16 +1918,16 @@
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C47" s="2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G47" s="2">
         <v>2</v>
@@ -1917,16 +1935,16 @@
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C48" s="2">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G48" s="2">
         <v>3</v>
@@ -1934,16 +1952,16 @@
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C49" s="2">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D49" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E49" s="7" t="s">
-        <v>51</v>
-      </c>
       <c r="F49" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -1951,16 +1969,16 @@
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C50" s="2">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G50" s="2">
         <v>2</v>
@@ -1968,89 +1986,224 @@
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C51" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G51" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="3:7">
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C52" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="3:7">
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C53" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G53" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="3:7">
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C54" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G54" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="7:7">
-      <c r="G67" s="6"/>
-    </row>
-    <row r="68" customHeight="1" spans="7:7">
-      <c r="G68" s="6"/>
-    </row>
-    <row r="69" customHeight="1" spans="7:7">
-      <c r="G69" s="6"/>
-    </row>
-    <row r="70" customHeight="1" spans="7:7">
-      <c r="G70" s="6"/>
-    </row>
-    <row r="71" customHeight="1" spans="7:7">
-      <c r="G71" s="6"/>
-    </row>
-    <row r="72" customHeight="1" spans="7:7">
-      <c r="G72" s="6"/>
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C55" s="2">
+        <v>40</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G55" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C56" s="2">
+        <v>41</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G56" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C57" s="2">
+        <v>42</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G57" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:7">
+      <c r="C58" s="2">
+        <v>43</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G58" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:7">
+      <c r="C59" s="2">
+        <v>44</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G59" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:7">
+      <c r="C60" s="2">
+        <v>45</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G60" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:7">
+      <c r="C61" s="2">
+        <v>46</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G61" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:7">
+      <c r="C62" s="2">
+        <v>47</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G62" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:7">
+      <c r="C63" s="2">
+        <v>48</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G63" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="73" customHeight="1" spans="7:7">
       <c r="G73" s="6"/>
@@ -2061,14 +2214,32 @@
     <row r="75" customHeight="1" spans="7:7">
       <c r="G75" s="6"/>
     </row>
-    <row r="92" customHeight="1" spans="7:7">
-      <c r="G92" s="6"/>
-    </row>
-    <row r="93" customHeight="1" spans="7:7">
-      <c r="G93" s="6"/>
-    </row>
-    <row r="94" customHeight="1" spans="7:7">
-      <c r="G94" s="6"/>
+    <row r="76" customHeight="1" spans="7:7">
+      <c r="G76" s="6"/>
+    </row>
+    <row r="77" customHeight="1" spans="7:7">
+      <c r="G77" s="6"/>
+    </row>
+    <row r="78" customHeight="1" spans="7:7">
+      <c r="G78" s="6"/>
+    </row>
+    <row r="79" customHeight="1" spans="7:7">
+      <c r="G79" s="6"/>
+    </row>
+    <row r="80" customHeight="1" spans="7:7">
+      <c r="G80" s="6"/>
+    </row>
+    <row r="81" customHeight="1" spans="7:7">
+      <c r="G81" s="6"/>
+    </row>
+    <row r="98" customHeight="1" spans="7:7">
+      <c r="G98" s="6"/>
+    </row>
+    <row r="99" customHeight="1" spans="7:7">
+      <c r="G99" s="6"/>
+    </row>
+    <row r="100" customHeight="1" spans="7:7">
+      <c r="G100" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="67">
   <si>
     <t>ID</t>
   </si>
@@ -173,6 +173,15 @@
     <t>13,35,19,2006,2003,32,52</t>
   </si>
   <si>
+    <t>13,33,24,2004,2003,32,53</t>
+  </si>
+  <si>
+    <t>13,34,24,2005,2003,32,53</t>
+  </si>
+  <si>
+    <t>13,35,24,2006,2003,32,53</t>
+  </si>
+  <si>
     <t>8,33,18,2004,2003,2001,50</t>
   </si>
   <si>
@@ -219,15 +228,6 @@
   </si>
   <si>
     <t>金色道魂50</t>
-  </si>
-  <si>
-    <t>13,33,24,2004,2003,32,53</t>
-  </si>
-  <si>
-    <t>13,34,24,2005,2003,32,53</t>
-  </si>
-  <si>
-    <t>13,35,24,2006,2003,32,53</t>
   </si>
 </sst>
 </file>
@@ -1204,7 +1204,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
@@ -1693,61 +1693,61 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" customHeight="1"/>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C32" s="2">
+        <v>107</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G32" s="2">
+        <v>1</v>
+      </c>
+    </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C33" s="2">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>37</v>
       </c>
       <c r="G33" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C34" s="2">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>37</v>
       </c>
       <c r="G34" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C35" s="2">
-        <v>21</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G35" s="2">
         <v>3</v>
       </c>
     </row>
+    <row r="35" s="2" customFormat="1" customHeight="1"/>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C36" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>35</v>
@@ -1764,7 +1764,7 @@
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C37" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>38</v>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C38" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>40</v>
@@ -1798,7 +1798,7 @@
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C39" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>35</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C40" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>38</v>
@@ -1832,7 +1832,7 @@
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C41" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>40</v>
@@ -1849,7 +1849,7 @@
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C42" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>35</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C43" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>38</v>
@@ -1883,7 +1883,7 @@
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C44" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>40</v>
@@ -1898,70 +1898,70 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" s="2" customFormat="1" customHeight="1"/>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C45" s="2">
+        <v>28</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G45" s="2">
+        <v>1</v>
+      </c>
+    </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C46" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="G46" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C47" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E47" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E47" s="7" t="s">
-        <v>49</v>
-      </c>
       <c r="F47" s="7" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="G47" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C48" s="2">
-        <v>33</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G48" s="2">
         <v>3</v>
       </c>
     </row>
+    <row r="48" s="2" customFormat="1" customHeight="1"/>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C49" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -1969,16 +1969,16 @@
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C50" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G50" s="2">
         <v>2</v>
@@ -1986,16 +1986,16 @@
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C51" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G51" s="2">
         <v>3</v>
@@ -2003,16 +2003,16 @@
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C52" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -2020,16 +2020,16 @@
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C53" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G53" s="2">
         <v>2</v>
@@ -2037,16 +2037,16 @@
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C54" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G54" s="2">
         <v>3</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C55" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -2071,16 +2071,16 @@
     </row>
     <row r="56" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C56" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G56" s="2">
         <v>2</v>
@@ -2088,67 +2088,67 @@
     </row>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C57" s="2">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G57" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="3:7">
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C58" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E58" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E58" s="7" t="s">
-        <v>45</v>
-      </c>
       <c r="F58" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="3:7">
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C59" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G59" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="3:7">
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:7">
       <c r="C60" s="2">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G60" s="2">
         <v>3</v>
@@ -2156,16 +2156,16 @@
     </row>
     <row r="61" customHeight="1" spans="3:7">
       <c r="C61" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E61" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F61" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>61</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -2173,16 +2173,16 @@
     </row>
     <row r="62" customHeight="1" spans="3:7">
       <c r="C62" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G62" s="2">
         <v>2</v>
@@ -2190,29 +2190,71 @@
     </row>
     <row r="63" customHeight="1" spans="3:7">
       <c r="C63" s="2">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G63" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="7:7">
-      <c r="G73" s="6"/>
-    </row>
-    <row r="74" customHeight="1" spans="7:7">
-      <c r="G74" s="6"/>
-    </row>
-    <row r="75" customHeight="1" spans="7:7">
-      <c r="G75" s="6"/>
+    <row r="64" customHeight="1" spans="3:7">
+      <c r="C64" s="2">
+        <v>46</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G64" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:7">
+      <c r="C65" s="2">
+        <v>47</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G65" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:7">
+      <c r="C66" s="2">
+        <v>48</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G66" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="76" customHeight="1" spans="7:7">
       <c r="G76" s="6"/>
@@ -2232,14 +2274,23 @@
     <row r="81" customHeight="1" spans="7:7">
       <c r="G81" s="6"/>
     </row>
-    <row r="98" customHeight="1" spans="7:7">
-      <c r="G98" s="6"/>
-    </row>
-    <row r="99" customHeight="1" spans="7:7">
-      <c r="G99" s="6"/>
-    </row>
-    <row r="100" customHeight="1" spans="7:7">
-      <c r="G100" s="6"/>
+    <row r="82" customHeight="1" spans="7:7">
+      <c r="G82" s="6"/>
+    </row>
+    <row r="83" customHeight="1" spans="7:7">
+      <c r="G83" s="6"/>
+    </row>
+    <row r="84" customHeight="1" spans="7:7">
+      <c r="G84" s="6"/>
+    </row>
+    <row r="101" customHeight="1" spans="7:7">
+      <c r="G101" s="6"/>
+    </row>
+    <row r="102" customHeight="1" spans="7:7">
+      <c r="G102" s="6"/>
+    </row>
+    <row r="103" customHeight="1" spans="7:7">
+      <c r="G103" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="85">
   <si>
     <t>ID</t>
   </si>
@@ -35,6 +35,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>ItemId</t>
+  </si>
+  <si>
     <t>AttrIdList</t>
   </si>
   <si>
@@ -228,6 +231,57 @@
   </si>
   <si>
     <t>金色道魂50</t>
+  </si>
+  <si>
+    <t>13,33,19,2004,2003,2001,52</t>
+  </si>
+  <si>
+    <t>13,34,19,2005,2003,2001,52</t>
+  </si>
+  <si>
+    <t>13,35,19,2006,2003,2001,52</t>
+  </si>
+  <si>
+    <t>13,33,24,2004,2003,2001,53</t>
+  </si>
+  <si>
+    <t>13,34,24,2005,2003,2001,53</t>
+  </si>
+  <si>
+    <t>13,35,24,2006,2003,2001,53</t>
+  </si>
+  <si>
+    <t>粉色50战士宠物</t>
+  </si>
+  <si>
+    <t>2003,2004,2007,2012,2001,31,2013,32,2010</t>
+  </si>
+  <si>
+    <t>50,50,50,50,50,50,50,50,50</t>
+  </si>
+  <si>
+    <t>粉色50法师宠物</t>
+  </si>
+  <si>
+    <t>2003,2005,2008,2012,2001,31,2013,32,2010</t>
+  </si>
+  <si>
+    <t>粉色50道士宠物</t>
+  </si>
+  <si>
+    <t>2003,2006,2009,2012,2001,31,2013,32,2010</t>
+  </si>
+  <si>
+    <t>粉色70战士宠物</t>
+  </si>
+  <si>
+    <t>70,70,70,70,70,70,70,70,70</t>
+  </si>
+  <si>
+    <t>粉色70法师宠物</t>
+  </si>
+  <si>
+    <t>粉色70道士宠物</t>
   </si>
 </sst>
 </file>
@@ -251,12 +305,6 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -273,6 +321,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -874,17 +928,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1204,1097 +1257,1401 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G103"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="A1:H90"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9" style="3"/>
-    <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.0833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="35.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="3" customWidth="1"/>
-    <col min="9" max="16367" width="9" style="3"/>
-    <col min="16368" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9" style="2"/>
+    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.925" style="1" customWidth="1"/>
+    <col min="6" max="6" width="29.0833333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.75" style="2" customWidth="1"/>
+    <col min="10" max="16368" width="9" style="2"/>
+    <col min="16369" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:7">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:7">
-      <c r="A4" s="3"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5" t="s">
+      <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="5" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:7">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5" t="s">
+      <c r="H4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="4">
+        <v>8205</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="4">
+        <v>8205</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="C8" s="1">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="4">
+        <v>8205</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="C9" s="1">
+        <v>4</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="4">
+        <v>8205</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="C10" s="1">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="4">
+        <v>8205</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4">
+        <v>8205</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="D12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="4">
+        <v>8205</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C6" s="2">
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="4">
+        <v>8205</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="4">
+        <v>8205</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1"/>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="C16" s="1">
+        <v>10</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="1">
+        <v>8206</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="7" t="s">
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C17" s="1">
         <v>11</v>
       </c>
-      <c r="G6" s="2">
+      <c r="D17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="1">
+        <v>8206</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C18" s="1">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="1">
+        <v>8206</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C19" s="1">
+        <v>13</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="1">
+        <v>8206</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C7" s="2">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C20" s="1">
+        <v>14</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="1">
+        <v>8206</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="2">
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C21" s="1">
+        <v>15</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="1">
+        <v>8206</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1"/>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C23" s="1">
+        <v>16</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C24" s="1">
+        <v>17</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C8" s="2">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C25" s="1">
+        <v>18</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H25" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="2">
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C26" s="1">
+        <v>101</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C27" s="1">
+        <v>102</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H27" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C28" s="1">
+        <v>103</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C9" s="2">
-        <v>4</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="2">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C29" s="1">
+        <v>104</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H29" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C10" s="2">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="2">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C30" s="1">
+        <v>105</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H30" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C11" s="2">
-        <v>6</v>
-      </c>
-      <c r="D11" s="2" t="s">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C31" s="1">
+        <v>106</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H31" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C32" s="1">
+        <v>107</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C33" s="1">
+        <v>108</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H33" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C34" s="1">
+        <v>109</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H34" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1"/>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C36" s="1">
         <v>19</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="2">
+      <c r="D36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C37" s="1">
+        <v>20</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H37" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C38" s="1">
+        <v>21</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H38" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C12" s="2">
-        <v>7</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="2">
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C39" s="1">
+        <v>22</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E39" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H39" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C13" s="2">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="2">
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C40" s="1">
+        <v>23</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H40" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C14" s="2">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="2">
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C41" s="1">
+        <v>24</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H41" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" customHeight="1"/>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C16" s="2">
-        <v>10</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="7" t="s">
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C42" s="1">
         <v>25</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="D42" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C43" s="1">
         <v>26</v>
       </c>
-      <c r="G16" s="2">
+      <c r="D43" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H43" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C44" s="1">
+        <v>27</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E44" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H44" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C45" s="1">
+        <v>28</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E45" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H45" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C17" s="2">
-        <v>11</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="2">
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C46" s="1">
+        <v>29</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E46" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H46" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C18" s="2">
-        <v>12</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="7" t="s">
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C47" s="1">
         <v>30</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="2">
+      <c r="D47" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E47" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H47" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C19" s="2">
-        <v>13</v>
-      </c>
-      <c r="D19" s="2" t="s">
+    <row r="48" s="1" customFormat="1" customHeight="1"/>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C49" s="1">
         <v>31</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="7" t="s">
+      <c r="D49" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C50" s="1">
         <v>32</v>
       </c>
-      <c r="G19" s="2">
+      <c r="D50" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E50" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H50" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C51" s="1">
+        <v>33</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E51" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H51" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C52" s="1">
+        <v>34</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H52" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C20" s="2">
-        <v>14</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" s="2">
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C53" s="1">
+        <v>35</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E53" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H53" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C21" s="2">
-        <v>15</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="2">
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C54" s="1">
+        <v>36</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E54" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H54" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" customHeight="1"/>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C23" s="2">
-        <v>16</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="7" t="s">
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C55" s="1">
         <v>37</v>
       </c>
-      <c r="G23" s="2">
+      <c r="D55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E55" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H55" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C24" s="2">
-        <v>17</v>
-      </c>
-      <c r="D24" s="2" t="s">
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C56" s="1">
         <v>38</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="D56" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E56" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H56" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C57" s="1">
         <v>39</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G24" s="2">
+      <c r="D57" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E57" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H57" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C58" s="1">
+        <v>40</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E58" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C59" s="1">
+        <v>41</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E59" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H59" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C25" s="2">
-        <v>18</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G25" s="2">
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C60" s="1">
+        <v>42</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E60" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H60" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C26" s="2">
-        <v>101</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="2">
+    <row r="61" customHeight="1" spans="3:8">
+      <c r="C61" s="1">
+        <v>43</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H61" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C27" s="2">
-        <v>102</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G27" s="2">
+    <row r="62" customHeight="1" spans="3:8">
+      <c r="C62" s="1">
+        <v>44</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E62" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C28" s="2">
-        <v>103</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G28" s="2">
+    <row r="63" customHeight="1" spans="3:8">
+      <c r="C63" s="1">
+        <v>45</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E63" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H63" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C29" s="2">
-        <v>104</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G29" s="2">
+    <row r="64" customHeight="1" spans="3:8">
+      <c r="C64" s="1">
+        <v>46</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E64" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H64" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C30" s="2">
-        <v>105</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G30" s="2">
+    <row r="65" customHeight="1" spans="3:8">
+      <c r="C65" s="1">
+        <v>47</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E65" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H65" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C31" s="2">
-        <v>106</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G31" s="2">
+    <row r="66" customHeight="1" spans="3:8">
+      <c r="C66" s="1">
+        <v>48</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E66" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H66" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C32" s="2">
-        <v>107</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G32" s="2">
+    <row r="69" customHeight="1" spans="3:8">
+      <c r="C69" s="1">
+        <v>201</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E69" s="1">
+        <v>8209</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H69" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C33" s="2">
-        <v>108</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G33" s="2">
+    <row r="70" customHeight="1" spans="3:8">
+      <c r="C70" s="1">
+        <v>202</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E70" s="1">
+        <v>8209</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H70" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C34" s="2">
-        <v>109</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G34" s="2">
+    <row r="71" customHeight="1" spans="3:8">
+      <c r="C71" s="1">
+        <v>203</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E71" s="1">
+        <v>8209</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H71" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="35" s="2" customFormat="1" customHeight="1"/>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C36" s="2">
-        <v>19</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G36" s="2">
+    <row r="73" customHeight="1" spans="3:8">
+      <c r="C73" s="1">
+        <v>211</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E73" s="1">
+        <v>8209</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H73" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C37" s="2">
-        <v>20</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G37" s="2">
+    <row r="74" customHeight="1" spans="3:8">
+      <c r="C74" s="1">
+        <v>212</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E74" s="1">
+        <v>8209</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H74" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C38" s="2">
-        <v>21</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G38" s="2">
+    <row r="75" customHeight="1" spans="3:8">
+      <c r="C75" s="1">
+        <v>213</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E75" s="1">
+        <v>8209</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H75" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C39" s="2">
-        <v>22</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G39" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C40" s="2">
-        <v>23</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G40" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C41" s="2">
-        <v>24</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G41" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C42" s="2">
-        <v>25</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G42" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C43" s="2">
-        <v>26</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G43" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C44" s="2">
-        <v>27</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G44" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C45" s="2">
-        <v>28</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G45" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C46" s="2">
-        <v>29</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G46" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C47" s="2">
-        <v>30</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G47" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1"/>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C49" s="2">
-        <v>31</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G49" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C50" s="2">
-        <v>32</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G50" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C51" s="2">
-        <v>33</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G51" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C52" s="2">
-        <v>34</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G52" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C53" s="2">
-        <v>35</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G53" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C54" s="2">
-        <v>36</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G54" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C55" s="2">
-        <v>37</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G55" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C56" s="2">
-        <v>38</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G56" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C57" s="2">
-        <v>39</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G57" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C58" s="2">
-        <v>40</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G58" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C59" s="2">
-        <v>41</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G59" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C60" s="2">
-        <v>42</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G60" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:7">
-      <c r="C61" s="2">
-        <v>43</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G61" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:7">
-      <c r="C62" s="2">
-        <v>44</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G62" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:7">
-      <c r="C63" s="2">
-        <v>45</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G63" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:7">
-      <c r="C64" s="2">
-        <v>46</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G64" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:7">
-      <c r="C65" s="2">
-        <v>47</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G65" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:7">
-      <c r="C66" s="2">
-        <v>48</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G66" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="7:7">
-      <c r="G76" s="6"/>
-    </row>
-    <row r="77" customHeight="1" spans="7:7">
-      <c r="G77" s="6"/>
-    </row>
-    <row r="78" customHeight="1" spans="7:7">
-      <c r="G78" s="6"/>
-    </row>
-    <row r="79" customHeight="1" spans="7:7">
-      <c r="G79" s="6"/>
-    </row>
-    <row r="80" customHeight="1" spans="7:7">
-      <c r="G80" s="6"/>
-    </row>
-    <row r="81" customHeight="1" spans="7:7">
-      <c r="G81" s="6"/>
-    </row>
-    <row r="82" customHeight="1" spans="7:7">
-      <c r="G82" s="6"/>
-    </row>
-    <row r="83" customHeight="1" spans="7:7">
-      <c r="G83" s="6"/>
-    </row>
-    <row r="84" customHeight="1" spans="7:7">
-      <c r="G84" s="6"/>
-    </row>
-    <row r="101" customHeight="1" spans="7:7">
-      <c r="G101" s="6"/>
-    </row>
-    <row r="102" customHeight="1" spans="7:7">
-      <c r="G102" s="6"/>
-    </row>
-    <row r="103" customHeight="1" spans="7:7">
-      <c r="G103" s="6"/>
+    <row r="78" customHeight="1" spans="3:8">
+      <c r="F78" s="5"/>
+    </row>
+    <row r="79" customHeight="1" spans="3:8">
+      <c r="F79" s="5"/>
+    </row>
+    <row r="80" customHeight="1" spans="3:8">
+      <c r="F80" s="5"/>
+    </row>
+    <row r="81" customHeight="1" spans="6:6">
+      <c r="F81" s="5"/>
+    </row>
+    <row r="82" customHeight="1" spans="6:6">
+      <c r="F82" s="5"/>
+    </row>
+    <row r="83" customHeight="1" spans="6:6">
+      <c r="F83" s="5"/>
+    </row>
+    <row r="84" customHeight="1" spans="6:6">
+      <c r="F84" s="5"/>
+    </row>
+    <row r="85" customHeight="1" spans="6:6">
+      <c r="F85" s="5"/>
+    </row>
+    <row r="86" customHeight="1" spans="6:6">
+      <c r="F86" s="5"/>
+    </row>
+    <row r="87" customHeight="1" spans="6:6">
+      <c r="F87" s="5"/>
+    </row>
+    <row r="88" customHeight="1" spans="6:6">
+      <c r="F88" s="5"/>
+    </row>
+    <row r="89" customHeight="1" spans="6:6">
+      <c r="F89" s="5"/>
+    </row>
+    <row r="90" customHeight="1" spans="6:6">
+      <c r="F90" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="82">
   <si>
     <t>ID</t>
   </si>
@@ -240,15 +240,6 @@
   </si>
   <si>
     <t>13,35,19,2006,2003,2001,52</t>
-  </si>
-  <si>
-    <t>13,33,24,2004,2003,2001,53</t>
-  </si>
-  <si>
-    <t>13,34,24,2005,2003,2001,53</t>
-  </si>
-  <si>
-    <t>13,35,24,2006,2003,2001,53</t>
   </si>
   <si>
     <t>粉色50战士宠物</t>
@@ -1257,7 +1248,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2441,7 +2432,7 @@
         <v>8207</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>65</v>
@@ -2461,7 +2452,7 @@
         <v>8207</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>65</v>
@@ -2481,7 +2472,7 @@
         <v>8207</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>65</v>
@@ -2490,131 +2481,185 @@
         <v>3</v>
       </c>
     </row>
+    <row r="67" customHeight="1" spans="3:8">
+      <c r="C67" s="1">
+        <v>49</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E67" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H67" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:8">
+      <c r="C68" s="1">
+        <v>50</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E68" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H68" s="1">
+        <v>2</v>
+      </c>
+    </row>
     <row r="69" customHeight="1" spans="3:8">
       <c r="C69" s="1">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E69" s="1">
-        <v>8209</v>
+        <v>8207</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="H69" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:8">
-      <c r="C70" s="1">
-        <v>202</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E70" s="1">
-        <v>8209</v>
-      </c>
-      <c r="F70" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H70" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:8">
       <c r="C71" s="1">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E71" s="1">
         <v>8209</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H71" s="1">
-        <v>3</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:8">
+      <c r="C72" s="1">
+        <v>202</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E72" s="1">
+        <v>8209</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H72" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:8">
       <c r="C73" s="1">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E73" s="1">
         <v>8209</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="H73" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:8">
-      <c r="C74" s="1">
-        <v>212</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E74" s="1">
-        <v>8209</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H74" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:8">
       <c r="C75" s="1">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E75" s="1">
         <v>8209</v>
       </c>
       <c r="F75" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H75" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:8">
+      <c r="C76" s="1">
+        <v>212</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G75" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H75" s="1">
+      <c r="E76" s="1">
+        <v>8209</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H76" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:8">
+      <c r="C77" s="1">
+        <v>213</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E77" s="1">
+        <v>8209</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H77" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="78" customHeight="1" spans="3:8">
-      <c r="F78" s="5"/>
-    </row>
-    <row r="79" customHeight="1" spans="3:8">
-      <c r="F79" s="5"/>
     </row>
     <row r="80" customHeight="1" spans="3:8">
       <c r="F80" s="5"/>
@@ -2648,6 +2693,12 @@
     </row>
     <row r="90" customHeight="1" spans="6:6">
       <c r="F90" s="5"/>
+    </row>
+    <row r="91" customHeight="1" spans="6:6">
+      <c r="F91" s="5"/>
+    </row>
+    <row r="92" customHeight="1" spans="6:6">
+      <c r="F92" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -125,16 +125,25 @@
     <t>7,35,18,2006,2003,2001</t>
   </si>
   <si>
-    <t>红色战魂45</t>
-  </si>
-  <si>
-    <t>45,45,45,45,45,45</t>
-  </si>
-  <si>
-    <t>红色法魂45</t>
-  </si>
-  <si>
-    <t>红色道魂45</t>
+    <t>金色战魂30</t>
+  </si>
+  <si>
+    <t>8,33,18,2004,2003,2001,50</t>
+  </si>
+  <si>
+    <t>30,30,30,30,30,30,30</t>
+  </si>
+  <si>
+    <t>金色法魂30</t>
+  </si>
+  <si>
+    <t>8,34,18,2005,2003,2001,50</t>
+  </si>
+  <si>
+    <t>金色道魂30</t>
+  </si>
+  <si>
+    <t>8,35,18,2006,2003,2001,50</t>
   </si>
   <si>
     <t>金色战魂40</t>
@@ -183,15 +192,6 @@
   </si>
   <si>
     <t>13,35,24,2006,2003,32,53</t>
-  </si>
-  <si>
-    <t>8,33,18,2004,2003,2001,50</t>
-  </si>
-  <si>
-    <t>8,34,18,2005,2003,2001,50</t>
-  </si>
-  <si>
-    <t>8,35,18,2006,2003,2001,50</t>
   </si>
   <si>
     <t>7,33,18,2004,2003,2001,50</t>
@@ -1586,13 +1586,13 @@
         <v>32</v>
       </c>
       <c r="E19" s="1">
-        <v>8206</v>
+        <v>8207</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
@@ -1603,16 +1603,16 @@
         <v>14</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="E20" s="1">
-        <v>8206</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="H20" s="1">
         <v>2</v>
@@ -1623,16 +1623,16 @@
         <v>15</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E21" s="1">
-        <v>8206</v>
+        <v>8207</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H21" s="1">
         <v>3</v>
@@ -1644,16 +1644,16 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E23" s="1">
         <v>8207</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H23" s="1">
         <v>1</v>
@@ -1664,16 +1664,16 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E24" s="1">
         <v>8207</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H24" s="1">
         <v>2</v>
@@ -1684,16 +1684,16 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="E25" s="1">
-        <v>8207</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="H25" s="1">
         <v>3</v>
@@ -1704,16 +1704,16 @@
         <v>101</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E26" s="1">
         <v>8207</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H26" s="1">
         <v>1</v>
@@ -1724,16 +1724,16 @@
         <v>102</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E27" s="1">
         <v>8207</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H27" s="1">
         <v>2</v>
@@ -1744,16 +1744,16 @@
         <v>103</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="E28" s="1">
-        <v>8207</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="H28" s="1">
         <v>3</v>
@@ -1764,16 +1764,16 @@
         <v>104</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E29" s="1">
         <v>8207</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H29" s="1">
         <v>1</v>
@@ -1784,16 +1784,16 @@
         <v>105</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E30" s="1">
         <v>8207</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H30" s="1">
         <v>2</v>
@@ -1804,16 +1804,16 @@
         <v>106</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G31" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="E31" s="1">
-        <v>8207</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="H31" s="1">
         <v>3</v>
@@ -1824,16 +1824,16 @@
         <v>107</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E32" s="1">
         <v>8207</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H32" s="1">
         <v>1</v>
@@ -1844,16 +1844,16 @@
         <v>108</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E33" s="1">
         <v>8207</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H33" s="1">
         <v>2</v>
@@ -1864,16 +1864,16 @@
         <v>109</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="E34" s="1">
-        <v>8207</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="H34" s="1">
         <v>3</v>
@@ -1885,16 +1885,16 @@
         <v>19</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E36" s="1">
         <v>8207</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H36" s="1">
         <v>1</v>
@@ -1905,16 +1905,16 @@
         <v>20</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E37" s="1">
         <v>8207</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H37" s="1">
         <v>2</v>
@@ -1925,16 +1925,16 @@
         <v>21</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" s="1">
+        <v>8207</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="E38" s="1">
-        <v>8207</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="H38" s="1">
         <v>3</v>
@@ -1945,7 +1945,7 @@
         <v>22</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E39" s="1">
         <v>8207</v>
@@ -1954,7 +1954,7 @@
         <v>55</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H39" s="1">
         <v>1</v>
@@ -1965,7 +1965,7 @@
         <v>23</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E40" s="1">
         <v>8207</v>
@@ -1974,7 +1974,7 @@
         <v>56</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H40" s="1">
         <v>2</v>
@@ -1985,7 +1985,7 @@
         <v>24</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E41" s="1">
         <v>8207</v>
@@ -1994,7 +1994,7 @@
         <v>57</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H41" s="1">
         <v>3</v>
@@ -2005,7 +2005,7 @@
         <v>25</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E42" s="1">
         <v>8207</v>
@@ -2014,7 +2014,7 @@
         <v>58</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H42" s="1">
         <v>1</v>
@@ -2025,7 +2025,7 @@
         <v>26</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E43" s="1">
         <v>8207</v>
@@ -2034,7 +2034,7 @@
         <v>59</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H43" s="1">
         <v>2</v>
@@ -2045,7 +2045,7 @@
         <v>27</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E44" s="1">
         <v>8207</v>
@@ -2054,7 +2054,7 @@
         <v>60</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H44" s="1">
         <v>3</v>
@@ -2065,7 +2065,7 @@
         <v>28</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E45" s="1">
         <v>8207</v>
@@ -2074,7 +2074,7 @@
         <v>61</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H45" s="1">
         <v>1</v>
@@ -2085,7 +2085,7 @@
         <v>29</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E46" s="1">
         <v>8207</v>
@@ -2094,7 +2094,7 @@
         <v>62</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H46" s="1">
         <v>2</v>
@@ -2105,7 +2105,7 @@
         <v>30</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E47" s="1">
         <v>8207</v>
@@ -2114,7 +2114,7 @@
         <v>63</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H47" s="1">
         <v>3</v>
@@ -2132,7 +2132,7 @@
         <v>8207</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>65</v>
@@ -2152,7 +2152,7 @@
         <v>8207</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>65</v>
@@ -2172,7 +2172,7 @@
         <v>8207</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>65</v>
@@ -2432,7 +2432,7 @@
         <v>8207</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>65</v>
@@ -2452,7 +2452,7 @@
         <v>8207</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>65</v>
@@ -2472,7 +2472,7 @@
         <v>8207</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>65</v>
@@ -2492,7 +2492,7 @@
         <v>8207</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>65</v>
@@ -2512,7 +2512,7 @@
         <v>8207</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G68" s="6" t="s">
         <v>65</v>
@@ -2532,7 +2532,7 @@
         <v>8207</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>65</v>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -92,37 +92,37 @@
     <t>橙色道魂45</t>
   </si>
   <si>
-    <t>橙色战魂50</t>
-  </si>
-  <si>
-    <t>50,50,50,50,50</t>
-  </si>
-  <si>
-    <t>橙色法魂50</t>
-  </si>
-  <si>
-    <t>橙色道魂50</t>
+    <t>红色战魂50</t>
+  </si>
+  <si>
+    <t>7,33,18,2004,2003,2001</t>
+  </si>
+  <si>
+    <t>50,50,50,50,50,50</t>
+  </si>
+  <si>
+    <t>红色法魂50</t>
+  </si>
+  <si>
+    <t>7,34,18,2005,2003,2001</t>
+  </si>
+  <si>
+    <t>红色道魂50</t>
+  </si>
+  <si>
+    <t>7,35,18,2006,2003,2001</t>
   </si>
   <si>
     <t>红色战魂40</t>
   </si>
   <si>
-    <t>7,33,18,2004,2003,2001</t>
-  </si>
-  <si>
     <t>40,40,40,40,40,40</t>
   </si>
   <si>
     <t>红色法魂40</t>
   </si>
   <si>
-    <t>7,34,18,2005,2003,2001</t>
-  </si>
-  <si>
     <t>红色道魂40</t>
-  </si>
-  <si>
-    <t>7,35,18,2006,2003,2001</t>
   </si>
   <si>
     <t>金色战魂30</t>
@@ -1464,14 +1464,14 @@
       <c r="D12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="4">
-        <v>8205</v>
+      <c r="E12" s="1">
+        <v>8206</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
@@ -1482,16 +1482,16 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="1">
+        <v>8206</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="E13" s="4">
-        <v>8205</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="H13" s="1">
         <v>2</v>
@@ -1502,16 +1502,16 @@
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="4">
-        <v>8205</v>
+        <v>26</v>
+      </c>
+      <c r="E14" s="1">
+        <v>8206</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H14" s="1">
         <v>3</v>
@@ -1523,16 +1523,16 @@
         <v>10</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E16" s="1">
         <v>8206</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
@@ -1543,16 +1543,16 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E17" s="1">
         <v>8206</v>
       </c>
       <c r="F17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="H17" s="1">
         <v>2</v>
@@ -1563,16 +1563,16 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E18" s="1">
         <v>8206</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H18" s="1">
         <v>3</v>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -2432,7 +2432,7 @@
         <v>8207</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>65</v>
@@ -2452,7 +2452,7 @@
         <v>8207</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>65</v>
@@ -2472,7 +2472,7 @@
         <v>8207</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>65</v>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="89">
   <si>
     <t>ID</t>
   </si>
@@ -273,6 +273,27 @@
   </si>
   <si>
     <t>粉色70道士宠物</t>
+  </si>
+  <si>
+    <t>暗金50战士坐骑</t>
+  </si>
+  <si>
+    <t>2003,2004,2007,2012,2001,31,2013,32</t>
+  </si>
+  <si>
+    <t>暗金50法师坐骑</t>
+  </si>
+  <si>
+    <t>暗金50道士坐骑</t>
+  </si>
+  <si>
+    <t>暗金70战士坐骑</t>
+  </si>
+  <si>
+    <t>暗金70法师坐骑</t>
+  </si>
+  <si>
+    <t>暗金70道士坐骑</t>
   </si>
 </sst>
 </file>
@@ -2662,42 +2683,141 @@
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:8">
-      <c r="F80" s="5"/>
-    </row>
-    <row r="81" customHeight="1" spans="6:6">
-      <c r="F81" s="5"/>
-    </row>
-    <row r="82" customHeight="1" spans="6:6">
-      <c r="F82" s="5"/>
-    </row>
-    <row r="83" customHeight="1" spans="6:6">
-      <c r="F83" s="5"/>
-    </row>
-    <row r="84" customHeight="1" spans="6:6">
-      <c r="F84" s="5"/>
-    </row>
-    <row r="85" customHeight="1" spans="6:6">
-      <c r="F85" s="5"/>
-    </row>
-    <row r="86" customHeight="1" spans="6:6">
-      <c r="F86" s="5"/>
-    </row>
-    <row r="87" customHeight="1" spans="6:6">
+      <c r="C80" s="1">
+        <v>901</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E80" s="1">
+        <v>8308</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H80" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:8">
+      <c r="C81" s="1">
+        <v>902</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E81" s="1">
+        <v>8308</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H81" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:8">
+      <c r="C82" s="1">
+        <v>903</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E82" s="1">
+        <v>8308</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H82" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:8">
+      <c r="C84" s="1">
+        <v>911</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E84" s="1">
+        <v>8308</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H84" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:8">
+      <c r="C85" s="1">
+        <v>912</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E85" s="1">
+        <v>8308</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H85" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:8">
+      <c r="C86" s="1">
+        <v>913</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E86" s="1">
+        <v>8308</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H86" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:8">
       <c r="F87" s="5"/>
     </row>
-    <row r="88" customHeight="1" spans="6:6">
+    <row r="88" customHeight="1" spans="3:8">
       <c r="F88" s="5"/>
     </row>
-    <row r="89" customHeight="1" spans="6:6">
+    <row r="89" customHeight="1" spans="3:8">
       <c r="F89" s="5"/>
     </row>
-    <row r="90" customHeight="1" spans="6:6">
+    <row r="90" customHeight="1" spans="3:8">
       <c r="F90" s="5"/>
     </row>
-    <row r="91" customHeight="1" spans="6:6">
+    <row r="91" customHeight="1" spans="3:8">
       <c r="F91" s="5"/>
     </row>
-    <row r="92" customHeight="1" spans="6:6">
+    <row r="92" customHeight="1" spans="3:8">
       <c r="F92" s="5"/>
     </row>
   </sheetData>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="94">
   <si>
     <t>ID</t>
   </si>
@@ -273,6 +273,21 @@
   </si>
   <si>
     <t>粉色70道士宠物</t>
+  </si>
+  <si>
+    <t>金色40战士坐骑</t>
+  </si>
+  <si>
+    <t>2003,2004,2007,2012,2001,31,2013</t>
+  </si>
+  <si>
+    <t>40,40,40,40,40,40,40,40</t>
+  </si>
+  <si>
+    <t>金色40法师坐骑</t>
+  </si>
+  <si>
+    <t>金色40道士坐骑</t>
   </si>
   <si>
     <t>暗金50战士坐骑</t>
@@ -1269,7 +1284,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2696,7 +2711,7 @@
         <v>83</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H80" s="1">
         <v>1</v>
@@ -2707,7 +2722,7 @@
         <v>902</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E81" s="1">
         <v>8308</v>
@@ -2716,7 +2731,7 @@
         <v>83</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H81" s="1">
         <v>2</v>
@@ -2727,7 +2742,7 @@
         <v>903</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E82" s="1">
         <v>8308</v>
@@ -2736,7 +2751,7 @@
         <v>83</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H82" s="1">
         <v>3</v>
@@ -2747,16 +2762,16 @@
         <v>911</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E84" s="1">
         <v>8308</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H84" s="1">
         <v>1</v>
@@ -2767,16 +2782,16 @@
         <v>912</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E85" s="1">
         <v>8308</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H85" s="1">
         <v>2</v>
@@ -2787,29 +2802,80 @@
         <v>913</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E86" s="1">
         <v>8308</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H86" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:8">
-      <c r="F87" s="5"/>
+      <c r="C87" s="1">
+        <v>914</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E87" s="1">
+        <v>8308</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H87" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" customHeight="1" spans="3:8">
-      <c r="F88" s="5"/>
+      <c r="C88" s="1">
+        <v>915</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E88" s="1">
+        <v>8308</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H88" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="89" customHeight="1" spans="3:8">
-      <c r="F89" s="5"/>
+      <c r="C89" s="1">
+        <v>916</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E89" s="1">
+        <v>8308</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H89" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="90" customHeight="1" spans="3:8">
       <c r="F90" s="5"/>
@@ -2819,6 +2885,15 @@
     </row>
     <row r="92" customHeight="1" spans="3:8">
       <c r="F92" s="5"/>
+    </row>
+    <row r="93" customHeight="1" spans="3:8">
+      <c r="F93" s="5"/>
+    </row>
+    <row r="94" customHeight="1" spans="3:8">
+      <c r="F94" s="5"/>
+    </row>
+    <row r="95" customHeight="1" spans="3:8">
+      <c r="F95" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -278,7 +278,7 @@
     <t>金色40战士坐骑</t>
   </si>
   <si>
-    <t>2003,2004,2007,2012,2001,31,2013</t>
+    <t>2003,2004,2007,2012,2001,31,32</t>
   </si>
   <si>
     <t>40,40,40,40,40,40,40,40</t>
@@ -293,7 +293,7 @@
     <t>暗金50战士坐骑</t>
   </si>
   <si>
-    <t>2003,2004,2007,2012,2001,31,2013,32</t>
+    <t>2003,2004,2007,2012,2001,31,32,2013</t>
   </si>
   <si>
     <t>暗金50法师坐骑</t>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="98">
   <si>
     <t>ID</t>
   </si>
@@ -287,9 +287,15 @@
     <t>金色40法师坐骑</t>
   </si>
   <si>
+    <t>2003,2005,2008,2012,2001,31,32</t>
+  </si>
+  <si>
     <t>金色40道士坐骑</t>
   </si>
   <si>
+    <t>2003,2006,2009,2012,2001,31,32</t>
+  </si>
+  <si>
     <t>暗金50战士坐骑</t>
   </si>
   <si>
@@ -299,7 +305,13 @@
     <t>暗金50法师坐骑</t>
   </si>
   <si>
+    <t>2003,2005,2008,2012,2001,31,32,2013</t>
+  </si>
+  <si>
     <t>暗金50道士坐骑</t>
+  </si>
+  <si>
+    <t>2003,2006,2009,2012,2001,31,32,2013</t>
   </si>
   <si>
     <t>暗金70战士坐骑</t>
@@ -2728,7 +2740,7 @@
         <v>8308</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>84</v>
@@ -2742,13 +2754,13 @@
         <v>903</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E82" s="1">
         <v>8308</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G82" s="6" t="s">
         <v>84</v>
@@ -2762,13 +2774,13 @@
         <v>911</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E84" s="1">
         <v>8308</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G84" s="6" t="s">
         <v>73</v>
@@ -2782,13 +2794,13 @@
         <v>912</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E85" s="1">
         <v>8308</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G85" s="6" t="s">
         <v>73</v>
@@ -2802,13 +2814,13 @@
         <v>913</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E86" s="1">
         <v>8308</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G86" s="6" t="s">
         <v>73</v>
@@ -2822,13 +2834,13 @@
         <v>914</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E87" s="1">
         <v>8308</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G87" s="6" t="s">
         <v>79</v>
@@ -2842,13 +2854,13 @@
         <v>915</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E88" s="1">
         <v>8308</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G88" s="6" t="s">
         <v>79</v>
@@ -2862,13 +2874,13 @@
         <v>916</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E89" s="1">
         <v>8308</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G89" s="6" t="s">
         <v>79</v>
